--- a/タスク管理_坂木信太.xlsx
+++ b/タスク管理_坂木信太.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629407C1-3751-41AB-A257-C68336949237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C822595A-A589-4223-B593-6BDFF608524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E876E417-BC45-4760-A2EC-6C45568681F6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
   <si>
     <t>No</t>
     <phoneticPr fontId="4"/>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>坂木</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>α版：プレイヤー・ボス・UIのスクリプト作成</t>
   </si>
   <si>
@@ -142,9 +138,6 @@
   </si>
   <si>
     <t>プレイヤーモデル・リグ（パーツ割り当て・IK）の組み込み</t>
-  </si>
-  <si>
-    <t>α版の動作確認・手触り調整（操作・足の動き・HUD）</t>
   </si>
   <si>
     <t>実施中</t>
@@ -165,9 +158,6 @@
     <t>武器・ガジェットの種類を決めて追加</t>
   </si>
   <si>
-    <t>拠点の実装（武器の購入・改造・強化）</t>
-  </si>
-  <si>
     <t>ボス撃破でウルト獲得（絡みつく根）・ウルトコンボ</t>
   </si>
   <si>
@@ -178,6 +168,24 @@
   </si>
   <si>
     <t>通しプレイ・バグ修正・仕上げ</t>
+  </si>
+  <si>
+    <t>坂木</t>
+  </si>
+  <si>
+    <t>α版の動作確認・手触り調整（操作・足の動き・HUD・握り方・しゃがみ）</t>
+  </si>
+  <si>
+    <t>ステージ7ラスボス（原初の魔法少女）のボス戦（α版）</t>
+  </si>
+  <si>
+    <t>ゲームの流れ（拠点⇔ステージのシーン遷移）・Assetsの整理</t>
+  </si>
+  <si>
+    <t>拠点の3Dメニュー（カメラ演出・ステージ選択・ホログラムの設計図）</t>
+  </si>
+  <si>
+    <t>拠点の中身（装備・強化・変更／武器作成・研究）</t>
   </si>
 </sst>
 </file>
@@ -278,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="67">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -921,41 +929,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.249977111117893"/>
@@ -979,30 +952,6 @@
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1089,19 +1038,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color theme="1"/>
       </left>
@@ -1146,7 +1082,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1252,9 +1188,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1267,8 +1200,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1285,110 +1230,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1428,6 +1274,69 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1608,10 +1517,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+        <xdr:cNvPr id="2" name="直線矢印コネクタ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BAB5A90-883E-20E1-80B5-961D1EF792A4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E128D6DC-4FF3-2FFD-E747-A4C8560D4C6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1665,10 +1574,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="直線矢印コネクタ 19">
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08775D00-4E8F-7861-0BF2-852F2F3528EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{340BB3A3-5AA2-6127-6678-72BCBFA950D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1722,10 +1631,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E82B562-DB95-E87F-7E09-A9AC5EE225D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AFD5B41-A245-74E2-8370-A4E40922CBC8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1779,10 +1688,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D828FED-38FE-5034-9FD7-44B3E9C145B8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A808755D-A4A8-2869-0D23-DCC9C6FA9E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1836,10 +1745,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D390456-15B8-BEF3-548E-D9F2A8FBD750}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4177036B-3EDF-3AEB-7242-C3824FD5FF69}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1886,17 +1795,17 @@
       <xdr:rowOff>533400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>279400</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>533400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56779E28-A3B0-82B1-9E62-F28C1408EACF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97071037-BE7B-A768-D4BF-E08399A1761F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1905,7 +1814,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10085070" y="3924300"/>
-          <a:ext cx="260350" cy="0"/>
+          <a:ext cx="565150" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1937,23 +1846,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="直線矢印コネクタ 24">
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81BF6E7-FB76-C71A-27C9-8A5CAB179989}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{050123E0-3815-9C92-0B90-D896F336EBA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1961,8 +1870,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12432030" y="4356100"/>
-          <a:ext cx="1974850" cy="0"/>
+          <a:off x="11586210" y="4356100"/>
+          <a:ext cx="237490" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1994,23 +1903,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="直線矢印コネクタ 25">
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53107B34-FCAE-C6AC-E0F3-89D61274EBAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7502FCD-BFE9-06EF-062B-259C0C8FA778}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2018,8 +1927,350 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14451330" y="5118100"/>
-          <a:ext cx="4222750" cy="0"/>
+          <a:off x="11586210" y="4686300"/>
+          <a:ext cx="237490" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7FC4203-69BC-EFD2-0C3E-E25CE6E20177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11868150" y="5118100"/>
+          <a:ext cx="237490" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="156082"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CD1C9F-D67B-F641-BAA0-44A50F9FF5A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11868150" y="5448300"/>
+          <a:ext cx="237490" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49FAAB91-3E38-C9E2-D411-097A398BD908}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11868150" y="5880100"/>
+          <a:ext cx="1083310" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="156082"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22F04FE1-02EF-66B2-A2C1-96C8FA41A0EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11868150" y="6210300"/>
+          <a:ext cx="519430" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線矢印コネクタ 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B88811F-63E5-1AA9-9374-9580D0A7F4C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12995910" y="6642100"/>
+          <a:ext cx="2020570" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="156082"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDD4E3D-A1DD-04B9-A0B6-2FDFB6CD2510}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15060930" y="7404100"/>
+          <a:ext cx="3613150" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2053,21 +2304,21 @@
     <xdr:from>
       <xdr:col>40</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>60</xdr:col>
       <xdr:colOff>279399</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{592776FB-BE8E-4B34-35B6-C2FE9566F06A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45E58281-FF10-08B6-6524-4F8462FD1B74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2075,7 +2326,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18718530" y="5880100"/>
+          <a:off x="18718530" y="8166100"/>
           <a:ext cx="6150609" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2110,21 +2361,21 @@
     <xdr:from>
       <xdr:col>61</xdr:col>
       <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>74</xdr:col>
       <xdr:colOff>256541</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+        <xdr:cNvPr id="34" name="直線矢印コネクタ 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A42758D-24AC-3556-38DE-9CD70C82072F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71EDC694-223B-E1D8-BDCB-92625DA66FE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2132,7 +2383,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24913589" y="6642100"/>
+          <a:off x="24913589" y="8928100"/>
           <a:ext cx="4177032" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2167,21 +2418,21 @@
     <xdr:from>
       <xdr:col>75</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>95</xdr:col>
       <xdr:colOff>279401</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+        <xdr:cNvPr id="35" name="直線矢印コネクタ 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9B18BF4-24D7-4F0A-A6B6-9CD9108FD9B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403E7230-2084-8EAC-4A31-B3A4960C8007}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2189,7 +2440,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29135071" y="7404100"/>
+          <a:off x="29135071" y="9690100"/>
           <a:ext cx="6333490" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2224,21 +2475,21 @@
     <xdr:from>
       <xdr:col>96</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>109</xdr:col>
       <xdr:colOff>279399</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+        <xdr:cNvPr id="36" name="直線矢印コネクタ 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8898B4A-2892-6722-F0C4-2F9F618E8530}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77DC16BF-1DC7-F695-C4F2-9B6B92307EC1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2246,7 +2497,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35513011" y="8166100"/>
+          <a:off x="35513011" y="10452100"/>
           <a:ext cx="4154168" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2281,21 +2532,21 @@
     <xdr:from>
       <xdr:col>110</xdr:col>
       <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>123</xdr:col>
       <xdr:colOff>279401</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="直線矢印コネクタ 30">
+        <xdr:cNvPr id="37" name="直線矢印コネクタ 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F6A0C82-D6E8-BC48-6774-A62DE1310460}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A54D43F-850B-8973-749E-C6E5474711AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2303,7 +2554,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="39711629" y="8928100"/>
+          <a:off x="39711629" y="11214100"/>
           <a:ext cx="4199892" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2338,21 +2589,21 @@
     <xdr:from>
       <xdr:col>124</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>137</xdr:col>
       <xdr:colOff>279401</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="直線矢印コネクタ 31">
+        <xdr:cNvPr id="38" name="直線矢印コネクタ 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBCC40D4-2460-9D5C-0561-46C1878A47F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B54CCD7B-866E-CA9E-6D55-5DA60EF0C1C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2360,7 +2611,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="43955971" y="9690100"/>
+          <a:off x="43955971" y="11976100"/>
           <a:ext cx="4222750" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2395,21 +2646,21 @@
     <xdr:from>
       <xdr:col>138</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>159</xdr:col>
       <xdr:colOff>279401</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
+        <xdr:cNvPr id="39" name="直線矢印コネクタ 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{819C3A76-1E74-F91B-5F69-CBA681FB090D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{292FD316-5D32-A9A4-598E-5F4AC9FAEBE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2417,7 +2668,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="48223171" y="10452100"/>
+          <a:off x="48223171" y="12738100"/>
           <a:ext cx="6661150" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2774,7 +3025,7 @@
     <col min="1" max="1" width="4.296875" style="28" customWidth="1"/>
     <col min="2" max="2" width="5.19921875" customWidth="1"/>
     <col min="3" max="3" width="30.796875" style="30" customWidth="1"/>
-    <col min="4" max="4" width="9.296875" style="36" customWidth="1"/>
+    <col min="4" max="4" width="9.296875" style="35" customWidth="1"/>
     <col min="5" max="8" width="15.796875" style="25" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="4.296875" bestFit="1" customWidth="1"/>
@@ -2801,7 +3052,7 @@
       <c r="A1" s="26"/>
       <c r="B1" s="1"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="38"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="23"/>
       <c r="F1" s="23"/>
       <c r="G1" s="23"/>
@@ -2992,48 +3243,48 @@
     </row>
     <row r="2" spans="1:192" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="26"/>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="76" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="60" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="78">
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="82">
         <v>46296</v>
       </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="80"/>
-      <c r="U2" s="60" t="s">
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="84"/>
+      <c r="U2" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="66"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
-      <c r="AE2" s="60" t="s">
+      <c r="AE2" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="62"/>
+      <c r="AF2" s="65"/>
+      <c r="AG2" s="65"/>
+      <c r="AH2" s="66"/>
       <c r="AJ2" s="1" t="s">
         <v>11</v>
       </c>
@@ -3193,33 +3444,33 @@
     </row>
     <row r="3" spans="1:192" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="26"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="60" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="78">
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="82">
         <v>46477</v>
       </c>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="80"/>
-      <c r="U3" s="60" t="s">
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="84"/>
+      <c r="U3" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="62"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
@@ -3390,7 +3641,7 @@
       <c r="A4" s="26"/>
       <c r="B4" s="1"/>
       <c r="C4" s="29"/>
-      <c r="D4" s="38"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
@@ -3583,441 +3834,441 @@
       <c r="A5" s="26"/>
       <c r="B5" s="1"/>
       <c r="C5" s="29"/>
-      <c r="D5" s="38"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="81">
+      <c r="J5" s="51">
         <v>2026</v>
       </c>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="81"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="81"/>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="81"/>
-      <c r="AO5" s="81"/>
-      <c r="AP5" s="81"/>
-      <c r="AQ5" s="81"/>
-      <c r="AR5" s="81"/>
-      <c r="AS5" s="81"/>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="81"/>
-      <c r="AV5" s="81"/>
-      <c r="AW5" s="81"/>
-      <c r="AX5" s="81"/>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="81"/>
-      <c r="BA5" s="81"/>
-      <c r="BB5" s="81"/>
-      <c r="BC5" s="81"/>
-      <c r="BD5" s="81"/>
-      <c r="BE5" s="81"/>
-      <c r="BF5" s="81"/>
-      <c r="BG5" s="81"/>
-      <c r="BH5" s="81"/>
-      <c r="BI5" s="81"/>
-      <c r="BJ5" s="81"/>
-      <c r="BK5" s="81"/>
-      <c r="BL5" s="81"/>
-      <c r="BM5" s="81"/>
-      <c r="BN5" s="81"/>
-      <c r="BO5" s="81"/>
-      <c r="BP5" s="81"/>
-      <c r="BQ5" s="81"/>
-      <c r="BR5" s="81"/>
-      <c r="BS5" s="81"/>
-      <c r="BT5" s="81"/>
-      <c r="BU5" s="81"/>
-      <c r="BV5" s="81"/>
-      <c r="BW5" s="81"/>
-      <c r="BX5" s="81"/>
-      <c r="BY5" s="81"/>
-      <c r="BZ5" s="81"/>
-      <c r="CA5" s="81"/>
-      <c r="CB5" s="81"/>
-      <c r="CC5" s="81"/>
-      <c r="CD5" s="81"/>
-      <c r="CE5" s="81"/>
-      <c r="CF5" s="81"/>
-      <c r="CG5" s="81"/>
-      <c r="CH5" s="81"/>
-      <c r="CI5" s="81"/>
-      <c r="CJ5" s="81"/>
-      <c r="CK5" s="81"/>
-      <c r="CL5" s="81"/>
-      <c r="CM5" s="81"/>
-      <c r="CN5" s="81"/>
-      <c r="CO5" s="81"/>
-      <c r="CP5" s="81"/>
-      <c r="CQ5" s="81"/>
-      <c r="CR5" s="81"/>
-      <c r="CS5" s="81"/>
-      <c r="CT5" s="81"/>
-      <c r="CU5" s="81"/>
-      <c r="CV5" s="81"/>
-      <c r="CW5" s="81"/>
-      <c r="CX5" s="81">
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="51"/>
+      <c r="AF5" s="51"/>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
+      <c r="AL5" s="51"/>
+      <c r="AM5" s="51"/>
+      <c r="AN5" s="51"/>
+      <c r="AO5" s="51"/>
+      <c r="AP5" s="51"/>
+      <c r="AQ5" s="51"/>
+      <c r="AR5" s="51"/>
+      <c r="AS5" s="51"/>
+      <c r="AT5" s="51"/>
+      <c r="AU5" s="51"/>
+      <c r="AV5" s="51"/>
+      <c r="AW5" s="51"/>
+      <c r="AX5" s="51"/>
+      <c r="AY5" s="51"/>
+      <c r="AZ5" s="51"/>
+      <c r="BA5" s="51"/>
+      <c r="BB5" s="51"/>
+      <c r="BC5" s="51"/>
+      <c r="BD5" s="51"/>
+      <c r="BE5" s="51"/>
+      <c r="BF5" s="51"/>
+      <c r="BG5" s="51"/>
+      <c r="BH5" s="51"/>
+      <c r="BI5" s="51"/>
+      <c r="BJ5" s="51"/>
+      <c r="BK5" s="51"/>
+      <c r="BL5" s="51"/>
+      <c r="BM5" s="51"/>
+      <c r="BN5" s="51"/>
+      <c r="BO5" s="51"/>
+      <c r="BP5" s="51"/>
+      <c r="BQ5" s="51"/>
+      <c r="BR5" s="51"/>
+      <c r="BS5" s="51"/>
+      <c r="BT5" s="51"/>
+      <c r="BU5" s="51"/>
+      <c r="BV5" s="51"/>
+      <c r="BW5" s="51"/>
+      <c r="BX5" s="51"/>
+      <c r="BY5" s="51"/>
+      <c r="BZ5" s="51"/>
+      <c r="CA5" s="51"/>
+      <c r="CB5" s="51"/>
+      <c r="CC5" s="51"/>
+      <c r="CD5" s="51"/>
+      <c r="CE5" s="51"/>
+      <c r="CF5" s="51"/>
+      <c r="CG5" s="51"/>
+      <c r="CH5" s="51"/>
+      <c r="CI5" s="51"/>
+      <c r="CJ5" s="51"/>
+      <c r="CK5" s="51"/>
+      <c r="CL5" s="51"/>
+      <c r="CM5" s="51"/>
+      <c r="CN5" s="51"/>
+      <c r="CO5" s="51"/>
+      <c r="CP5" s="51"/>
+      <c r="CQ5" s="51"/>
+      <c r="CR5" s="51"/>
+      <c r="CS5" s="51"/>
+      <c r="CT5" s="51"/>
+      <c r="CU5" s="51"/>
+      <c r="CV5" s="51"/>
+      <c r="CW5" s="51"/>
+      <c r="CX5" s="51">
         <v>2027</v>
       </c>
-      <c r="CY5" s="81"/>
-      <c r="CZ5" s="81"/>
-      <c r="DA5" s="81"/>
-      <c r="DB5" s="81"/>
-      <c r="DC5" s="81"/>
-      <c r="DD5" s="81"/>
-      <c r="DE5" s="81"/>
-      <c r="DF5" s="81"/>
-      <c r="DG5" s="81"/>
-      <c r="DH5" s="81"/>
-      <c r="DI5" s="81"/>
-      <c r="DJ5" s="81"/>
-      <c r="DK5" s="81"/>
-      <c r="DL5" s="81"/>
-      <c r="DM5" s="81"/>
-      <c r="DN5" s="81"/>
-      <c r="DO5" s="81"/>
-      <c r="DP5" s="81"/>
-      <c r="DQ5" s="81"/>
-      <c r="DR5" s="81"/>
-      <c r="DS5" s="81"/>
-      <c r="DT5" s="81"/>
-      <c r="DU5" s="81"/>
-      <c r="DV5" s="81"/>
-      <c r="DW5" s="81"/>
-      <c r="DX5" s="81"/>
-      <c r="DY5" s="81"/>
-      <c r="DZ5" s="81"/>
-      <c r="EA5" s="81"/>
-      <c r="EB5" s="81"/>
-      <c r="EC5" s="81"/>
-      <c r="ED5" s="81"/>
-      <c r="EE5" s="81"/>
-      <c r="EF5" s="81"/>
-      <c r="EG5" s="81"/>
-      <c r="EH5" s="81"/>
-      <c r="EI5" s="81"/>
-      <c r="EJ5" s="81"/>
-      <c r="EK5" s="81"/>
-      <c r="EL5" s="81"/>
-      <c r="EM5" s="81"/>
-      <c r="EN5" s="81"/>
-      <c r="EO5" s="81"/>
-      <c r="EP5" s="81"/>
-      <c r="EQ5" s="81"/>
-      <c r="ER5" s="81"/>
-      <c r="ES5" s="81"/>
-      <c r="ET5" s="81"/>
-      <c r="EU5" s="81"/>
-      <c r="EV5" s="81"/>
-      <c r="EW5" s="81"/>
-      <c r="EX5" s="81"/>
-      <c r="EY5" s="81"/>
-      <c r="EZ5" s="81"/>
-      <c r="FA5" s="81"/>
-      <c r="FB5" s="81"/>
-      <c r="FC5" s="81"/>
-      <c r="FD5" s="81"/>
-      <c r="FE5" s="81"/>
-      <c r="FF5" s="81"/>
-      <c r="FG5" s="81"/>
-      <c r="FH5" s="81"/>
-      <c r="FI5" s="81"/>
-      <c r="FJ5" s="81"/>
-      <c r="FK5" s="81"/>
-      <c r="FL5" s="81"/>
-      <c r="FM5" s="81"/>
-      <c r="FN5" s="81"/>
-      <c r="FO5" s="81"/>
-      <c r="FP5" s="81"/>
-      <c r="FQ5" s="81"/>
-      <c r="FR5" s="81"/>
-      <c r="FS5" s="81"/>
-      <c r="FT5" s="81"/>
-      <c r="FU5" s="81"/>
-      <c r="FV5" s="81"/>
-      <c r="FW5" s="81"/>
-      <c r="FX5" s="81"/>
-      <c r="FY5" s="81"/>
-      <c r="FZ5" s="81"/>
-      <c r="GA5" s="81"/>
-      <c r="GB5" s="81"/>
-      <c r="GC5" s="81"/>
-      <c r="GD5" s="81"/>
-      <c r="GE5" s="81"/>
-      <c r="GF5" s="81"/>
-      <c r="GG5" s="81"/>
-      <c r="GH5" s="81"/>
-      <c r="GI5" s="81"/>
+      <c r="CY5" s="51"/>
+      <c r="CZ5" s="51"/>
+      <c r="DA5" s="51"/>
+      <c r="DB5" s="51"/>
+      <c r="DC5" s="51"/>
+      <c r="DD5" s="51"/>
+      <c r="DE5" s="51"/>
+      <c r="DF5" s="51"/>
+      <c r="DG5" s="51"/>
+      <c r="DH5" s="51"/>
+      <c r="DI5" s="51"/>
+      <c r="DJ5" s="51"/>
+      <c r="DK5" s="51"/>
+      <c r="DL5" s="51"/>
+      <c r="DM5" s="51"/>
+      <c r="DN5" s="51"/>
+      <c r="DO5" s="51"/>
+      <c r="DP5" s="51"/>
+      <c r="DQ5" s="51"/>
+      <c r="DR5" s="51"/>
+      <c r="DS5" s="51"/>
+      <c r="DT5" s="51"/>
+      <c r="DU5" s="51"/>
+      <c r="DV5" s="51"/>
+      <c r="DW5" s="51"/>
+      <c r="DX5" s="51"/>
+      <c r="DY5" s="51"/>
+      <c r="DZ5" s="51"/>
+      <c r="EA5" s="51"/>
+      <c r="EB5" s="51"/>
+      <c r="EC5" s="51"/>
+      <c r="ED5" s="51"/>
+      <c r="EE5" s="51"/>
+      <c r="EF5" s="51"/>
+      <c r="EG5" s="51"/>
+      <c r="EH5" s="51"/>
+      <c r="EI5" s="51"/>
+      <c r="EJ5" s="51"/>
+      <c r="EK5" s="51"/>
+      <c r="EL5" s="51"/>
+      <c r="EM5" s="51"/>
+      <c r="EN5" s="51"/>
+      <c r="EO5" s="51"/>
+      <c r="EP5" s="51"/>
+      <c r="EQ5" s="51"/>
+      <c r="ER5" s="51"/>
+      <c r="ES5" s="51"/>
+      <c r="ET5" s="51"/>
+      <c r="EU5" s="51"/>
+      <c r="EV5" s="51"/>
+      <c r="EW5" s="51"/>
+      <c r="EX5" s="51"/>
+      <c r="EY5" s="51"/>
+      <c r="EZ5" s="51"/>
+      <c r="FA5" s="51"/>
+      <c r="FB5" s="51"/>
+      <c r="FC5" s="51"/>
+      <c r="FD5" s="51"/>
+      <c r="FE5" s="51"/>
+      <c r="FF5" s="51"/>
+      <c r="FG5" s="51"/>
+      <c r="FH5" s="51"/>
+      <c r="FI5" s="51"/>
+      <c r="FJ5" s="51"/>
+      <c r="FK5" s="51"/>
+      <c r="FL5" s="51"/>
+      <c r="FM5" s="51"/>
+      <c r="FN5" s="51"/>
+      <c r="FO5" s="51"/>
+      <c r="FP5" s="51"/>
+      <c r="FQ5" s="51"/>
+      <c r="FR5" s="51"/>
+      <c r="FS5" s="51"/>
+      <c r="FT5" s="51"/>
+      <c r="FU5" s="51"/>
+      <c r="FV5" s="51"/>
+      <c r="FW5" s="51"/>
+      <c r="FX5" s="51"/>
+      <c r="FY5" s="51"/>
+      <c r="FZ5" s="51"/>
+      <c r="GA5" s="51"/>
+      <c r="GB5" s="51"/>
+      <c r="GC5" s="51"/>
+      <c r="GD5" s="51"/>
+      <c r="GE5" s="51"/>
+      <c r="GF5" s="51"/>
+      <c r="GG5" s="51"/>
+      <c r="GH5" s="51"/>
+      <c r="GI5" s="51"/>
     </row>
     <row r="6" spans="1:192" x14ac:dyDescent="0.45">
       <c r="A6" s="26"/>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="85" t="s">
+      <c r="F6" s="72"/>
+      <c r="G6" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="69" t="s">
+      <c r="H6" s="56"/>
+      <c r="I6" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="89">
+      <c r="J6" s="59">
         <f>N2</f>
         <v>46296</v>
       </c>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="90"/>
-      <c r="AB6" s="90"/>
-      <c r="AC6" s="90"/>
-      <c r="AD6" s="90"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
-      <c r="AG6" s="90"/>
-      <c r="AH6" s="90"/>
-      <c r="AI6" s="90"/>
-      <c r="AJ6" s="90"/>
-      <c r="AK6" s="90"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="91"/>
-      <c r="AO6" s="92">
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="60"/>
+      <c r="U6" s="60"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60"/>
+      <c r="X6" s="60"/>
+      <c r="Y6" s="60"/>
+      <c r="Z6" s="60"/>
+      <c r="AA6" s="60"/>
+      <c r="AB6" s="60"/>
+      <c r="AC6" s="60"/>
+      <c r="AD6" s="60"/>
+      <c r="AE6" s="60"/>
+      <c r="AF6" s="60"/>
+      <c r="AG6" s="60"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AJ6" s="60"/>
+      <c r="AK6" s="60"/>
+      <c r="AL6" s="60"/>
+      <c r="AM6" s="60"/>
+      <c r="AN6" s="61"/>
+      <c r="AO6" s="62">
         <f t="shared" ref="AO6:BS6" si="0">IF(DAY(AO7)=1,AO7,"")</f>
         <v>46327</v>
       </c>
-      <c r="AP6" s="90"/>
-      <c r="AQ6" s="90"/>
-      <c r="AR6" s="90"/>
-      <c r="AS6" s="90"/>
-      <c r="AT6" s="90"/>
-      <c r="AU6" s="90"/>
-      <c r="AV6" s="90"/>
-      <c r="AW6" s="90"/>
-      <c r="AX6" s="90"/>
-      <c r="AY6" s="90"/>
-      <c r="AZ6" s="90"/>
-      <c r="BA6" s="90"/>
-      <c r="BB6" s="90"/>
-      <c r="BC6" s="90"/>
-      <c r="BD6" s="90"/>
-      <c r="BE6" s="90"/>
-      <c r="BF6" s="90"/>
-      <c r="BG6" s="90"/>
-      <c r="BH6" s="90"/>
-      <c r="BI6" s="90"/>
-      <c r="BJ6" s="90"/>
-      <c r="BK6" s="90"/>
-      <c r="BL6" s="90"/>
-      <c r="BM6" s="90"/>
-      <c r="BN6" s="90"/>
-      <c r="BO6" s="90"/>
-      <c r="BP6" s="90"/>
-      <c r="BQ6" s="90"/>
-      <c r="BR6" s="91"/>
-      <c r="BS6" s="92">
+      <c r="AP6" s="60"/>
+      <c r="AQ6" s="60"/>
+      <c r="AR6" s="60"/>
+      <c r="AS6" s="60"/>
+      <c r="AT6" s="60"/>
+      <c r="AU6" s="60"/>
+      <c r="AV6" s="60"/>
+      <c r="AW6" s="60"/>
+      <c r="AX6" s="60"/>
+      <c r="AY6" s="60"/>
+      <c r="AZ6" s="60"/>
+      <c r="BA6" s="60"/>
+      <c r="BB6" s="60"/>
+      <c r="BC6" s="60"/>
+      <c r="BD6" s="60"/>
+      <c r="BE6" s="60"/>
+      <c r="BF6" s="60"/>
+      <c r="BG6" s="60"/>
+      <c r="BH6" s="60"/>
+      <c r="BI6" s="60"/>
+      <c r="BJ6" s="60"/>
+      <c r="BK6" s="60"/>
+      <c r="BL6" s="60"/>
+      <c r="BM6" s="60"/>
+      <c r="BN6" s="60"/>
+      <c r="BO6" s="60"/>
+      <c r="BP6" s="60"/>
+      <c r="BQ6" s="60"/>
+      <c r="BR6" s="61"/>
+      <c r="BS6" s="62">
         <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="BT6" s="90"/>
-      <c r="BU6" s="90"/>
-      <c r="BV6" s="90"/>
-      <c r="BW6" s="90"/>
-      <c r="BX6" s="90"/>
-      <c r="BY6" s="90"/>
-      <c r="BZ6" s="90"/>
-      <c r="CA6" s="90"/>
-      <c r="CB6" s="90"/>
-      <c r="CC6" s="90"/>
-      <c r="CD6" s="90"/>
-      <c r="CE6" s="90"/>
-      <c r="CF6" s="90"/>
-      <c r="CG6" s="90"/>
-      <c r="CH6" s="90"/>
-      <c r="CI6" s="90"/>
-      <c r="CJ6" s="90"/>
-      <c r="CK6" s="90"/>
-      <c r="CL6" s="90"/>
-      <c r="CM6" s="90"/>
-      <c r="CN6" s="90"/>
-      <c r="CO6" s="90"/>
-      <c r="CP6" s="90"/>
-      <c r="CQ6" s="90"/>
-      <c r="CR6" s="90"/>
-      <c r="CS6" s="90"/>
-      <c r="CT6" s="90"/>
-      <c r="CU6" s="90"/>
-      <c r="CV6" s="90"/>
-      <c r="CW6" s="91"/>
-      <c r="CX6" s="92">
+      <c r="BT6" s="60"/>
+      <c r="BU6" s="60"/>
+      <c r="BV6" s="60"/>
+      <c r="BW6" s="60"/>
+      <c r="BX6" s="60"/>
+      <c r="BY6" s="60"/>
+      <c r="BZ6" s="60"/>
+      <c r="CA6" s="60"/>
+      <c r="CB6" s="60"/>
+      <c r="CC6" s="60"/>
+      <c r="CD6" s="60"/>
+      <c r="CE6" s="60"/>
+      <c r="CF6" s="60"/>
+      <c r="CG6" s="60"/>
+      <c r="CH6" s="60"/>
+      <c r="CI6" s="60"/>
+      <c r="CJ6" s="60"/>
+      <c r="CK6" s="60"/>
+      <c r="CL6" s="60"/>
+      <c r="CM6" s="60"/>
+      <c r="CN6" s="60"/>
+      <c r="CO6" s="60"/>
+      <c r="CP6" s="60"/>
+      <c r="CQ6" s="60"/>
+      <c r="CR6" s="60"/>
+      <c r="CS6" s="60"/>
+      <c r="CT6" s="60"/>
+      <c r="CU6" s="60"/>
+      <c r="CV6" s="60"/>
+      <c r="CW6" s="61"/>
+      <c r="CX6" s="62">
         <f t="shared" ref="CX6:EC6" si="1">IF(DAY(CX7)=1,CX7,"")</f>
         <v>46388</v>
       </c>
-      <c r="CY6" s="90"/>
-      <c r="CZ6" s="90"/>
-      <c r="DA6" s="90"/>
-      <c r="DB6" s="90"/>
-      <c r="DC6" s="90"/>
-      <c r="DD6" s="90"/>
-      <c r="DE6" s="90"/>
-      <c r="DF6" s="90"/>
-      <c r="DG6" s="90"/>
-      <c r="DH6" s="90"/>
-      <c r="DI6" s="90"/>
-      <c r="DJ6" s="90"/>
-      <c r="DK6" s="90"/>
-      <c r="DL6" s="90"/>
-      <c r="DM6" s="90"/>
-      <c r="DN6" s="90"/>
-      <c r="DO6" s="90"/>
-      <c r="DP6" s="90"/>
-      <c r="DQ6" s="90"/>
-      <c r="DR6" s="90"/>
-      <c r="DS6" s="90"/>
-      <c r="DT6" s="90"/>
-      <c r="DU6" s="90"/>
-      <c r="DV6" s="90"/>
-      <c r="DW6" s="90"/>
-      <c r="DX6" s="90"/>
-      <c r="DY6" s="90"/>
-      <c r="DZ6" s="90"/>
-      <c r="EA6" s="90"/>
-      <c r="EB6" s="91"/>
-      <c r="EC6" s="92">
+      <c r="CY6" s="60"/>
+      <c r="CZ6" s="60"/>
+      <c r="DA6" s="60"/>
+      <c r="DB6" s="60"/>
+      <c r="DC6" s="60"/>
+      <c r="DD6" s="60"/>
+      <c r="DE6" s="60"/>
+      <c r="DF6" s="60"/>
+      <c r="DG6" s="60"/>
+      <c r="DH6" s="60"/>
+      <c r="DI6" s="60"/>
+      <c r="DJ6" s="60"/>
+      <c r="DK6" s="60"/>
+      <c r="DL6" s="60"/>
+      <c r="DM6" s="60"/>
+      <c r="DN6" s="60"/>
+      <c r="DO6" s="60"/>
+      <c r="DP6" s="60"/>
+      <c r="DQ6" s="60"/>
+      <c r="DR6" s="60"/>
+      <c r="DS6" s="60"/>
+      <c r="DT6" s="60"/>
+      <c r="DU6" s="60"/>
+      <c r="DV6" s="60"/>
+      <c r="DW6" s="60"/>
+      <c r="DX6" s="60"/>
+      <c r="DY6" s="60"/>
+      <c r="DZ6" s="60"/>
+      <c r="EA6" s="60"/>
+      <c r="EB6" s="61"/>
+      <c r="EC6" s="62">
         <f t="shared" si="1"/>
         <v>46419</v>
       </c>
-      <c r="ED6" s="90"/>
-      <c r="EE6" s="90"/>
-      <c r="EF6" s="90"/>
-      <c r="EG6" s="90"/>
-      <c r="EH6" s="90"/>
-      <c r="EI6" s="90"/>
-      <c r="EJ6" s="90"/>
-      <c r="EK6" s="90"/>
-      <c r="EL6" s="90"/>
-      <c r="EM6" s="90"/>
-      <c r="EN6" s="90"/>
-      <c r="EO6" s="90"/>
-      <c r="EP6" s="90"/>
-      <c r="EQ6" s="90"/>
-      <c r="ER6" s="90"/>
-      <c r="ES6" s="90"/>
-      <c r="ET6" s="90"/>
-      <c r="EU6" s="90"/>
-      <c r="EV6" s="90"/>
-      <c r="EW6" s="90"/>
-      <c r="EX6" s="90"/>
-      <c r="EY6" s="90"/>
-      <c r="EZ6" s="90"/>
-      <c r="FA6" s="90"/>
-      <c r="FB6" s="90"/>
-      <c r="FC6" s="90"/>
-      <c r="FD6" s="91"/>
-      <c r="FE6" s="92">
+      <c r="ED6" s="60"/>
+      <c r="EE6" s="60"/>
+      <c r="EF6" s="60"/>
+      <c r="EG6" s="60"/>
+      <c r="EH6" s="60"/>
+      <c r="EI6" s="60"/>
+      <c r="EJ6" s="60"/>
+      <c r="EK6" s="60"/>
+      <c r="EL6" s="60"/>
+      <c r="EM6" s="60"/>
+      <c r="EN6" s="60"/>
+      <c r="EO6" s="60"/>
+      <c r="EP6" s="60"/>
+      <c r="EQ6" s="60"/>
+      <c r="ER6" s="60"/>
+      <c r="ES6" s="60"/>
+      <c r="ET6" s="60"/>
+      <c r="EU6" s="60"/>
+      <c r="EV6" s="60"/>
+      <c r="EW6" s="60"/>
+      <c r="EX6" s="60"/>
+      <c r="EY6" s="60"/>
+      <c r="EZ6" s="60"/>
+      <c r="FA6" s="60"/>
+      <c r="FB6" s="60"/>
+      <c r="FC6" s="60"/>
+      <c r="FD6" s="61"/>
+      <c r="FE6" s="62">
         <f t="shared" ref="FE6" si="2">IF(DAY(FE7)=1,FE7,"")</f>
         <v>46447</v>
       </c>
-      <c r="FF6" s="90"/>
-      <c r="FG6" s="90"/>
-      <c r="FH6" s="90"/>
-      <c r="FI6" s="90"/>
-      <c r="FJ6" s="90"/>
-      <c r="FK6" s="90"/>
-      <c r="FL6" s="90"/>
-      <c r="FM6" s="90"/>
-      <c r="FN6" s="90"/>
-      <c r="FO6" s="90"/>
-      <c r="FP6" s="90"/>
-      <c r="FQ6" s="90"/>
-      <c r="FR6" s="90"/>
-      <c r="FS6" s="90"/>
-      <c r="FT6" s="90"/>
-      <c r="FU6" s="90"/>
-      <c r="FV6" s="90"/>
-      <c r="FW6" s="90"/>
-      <c r="FX6" s="90"/>
-      <c r="FY6" s="90"/>
-      <c r="FZ6" s="90"/>
-      <c r="GA6" s="90"/>
-      <c r="GB6" s="90"/>
-      <c r="GC6" s="90"/>
-      <c r="GD6" s="90"/>
-      <c r="GE6" s="90"/>
-      <c r="GF6" s="90"/>
-      <c r="GG6" s="90"/>
-      <c r="GH6" s="90"/>
-      <c r="GI6" s="93"/>
+      <c r="FF6" s="60"/>
+      <c r="FG6" s="60"/>
+      <c r="FH6" s="60"/>
+      <c r="FI6" s="60"/>
+      <c r="FJ6" s="60"/>
+      <c r="FK6" s="60"/>
+      <c r="FL6" s="60"/>
+      <c r="FM6" s="60"/>
+      <c r="FN6" s="60"/>
+      <c r="FO6" s="60"/>
+      <c r="FP6" s="60"/>
+      <c r="FQ6" s="60"/>
+      <c r="FR6" s="60"/>
+      <c r="FS6" s="60"/>
+      <c r="FT6" s="60"/>
+      <c r="FU6" s="60"/>
+      <c r="FV6" s="60"/>
+      <c r="FW6" s="60"/>
+      <c r="FX6" s="60"/>
+      <c r="FY6" s="60"/>
+      <c r="FZ6" s="60"/>
+      <c r="GA6" s="60"/>
+      <c r="GB6" s="60"/>
+      <c r="GC6" s="60"/>
+      <c r="GD6" s="60"/>
+      <c r="GE6" s="60"/>
+      <c r="GF6" s="60"/>
+      <c r="GG6" s="60"/>
+      <c r="GH6" s="60"/>
+      <c r="GI6" s="63"/>
       <c r="GJ6" s="19"/>
     </row>
     <row r="7" spans="1:192" x14ac:dyDescent="0.45">
       <c r="A7" s="27"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="72" t="s">
+      <c r="B7" s="69"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="87" t="s">
+      <c r="G7" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="87" t="s">
+      <c r="H7" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="70"/>
+      <c r="I7" s="74"/>
       <c r="J7" s="12">
         <f>N2</f>
         <v>46296</v>
@@ -4749,14 +5000,14 @@
     </row>
     <row r="8" spans="1:192" x14ac:dyDescent="0.45">
       <c r="A8" s="26"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="71"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="75"/>
       <c r="J8" s="13" t="str">
         <f>TEXT(J7,"aaa")</f>
         <v>木</v>
@@ -5491,11 +5742,11 @@
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="39" t="s">
+      <c r="C9" s="50" t="s">
         <v>13</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E9" s="34">
         <v>46296</v>
@@ -5510,7 +5761,7 @@
         <v>46297</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J9" s="31"/>
       <c r="K9" s="11"/>
@@ -5700,11 +5951,11 @@
       <c r="B10" s="3">
         <v>2</v>
       </c>
-      <c r="C10" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>13</v>
+      <c r="C10" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="34">
         <v>46297</v>
@@ -5719,7 +5970,7 @@
         <v>46298</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J10" s="33"/>
       <c r="K10" s="4"/>
@@ -5906,642 +6157,654 @@
     </row>
     <row r="11" spans="1:192" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="26"/>
-      <c r="B11" s="9">
+      <c r="B11" s="3">
         <v>3</v>
       </c>
-      <c r="C11" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="53">
+      <c r="C11" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="34">
         <v>46298</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="24">
         <v>46305</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="34">
         <v>46298</v>
       </c>
-      <c r="H11" s="54"/>
-      <c r="I11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="44"/>
-      <c r="AE11" s="44"/>
-      <c r="AF11" s="44"/>
-      <c r="AG11" s="44"/>
-      <c r="AH11" s="44"/>
-      <c r="AI11" s="44"/>
-      <c r="AJ11" s="44"/>
-      <c r="AK11" s="44"/>
-      <c r="AL11" s="44"/>
-      <c r="AM11" s="44"/>
-      <c r="AN11" s="45"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="44"/>
-      <c r="AQ11" s="44"/>
-      <c r="AR11" s="44"/>
-      <c r="AS11" s="44"/>
-      <c r="AT11" s="44"/>
-      <c r="AU11" s="44"/>
-      <c r="AV11" s="44"/>
-      <c r="AW11" s="44"/>
-      <c r="AX11" s="44"/>
-      <c r="AY11" s="44"/>
-      <c r="AZ11" s="44"/>
-      <c r="BA11" s="44"/>
-      <c r="BB11" s="44"/>
-      <c r="BC11" s="44"/>
-      <c r="BD11" s="44"/>
-      <c r="BE11" s="44"/>
-      <c r="BF11" s="44"/>
-      <c r="BG11" s="44"/>
-      <c r="BH11" s="44"/>
-      <c r="BI11" s="44"/>
-      <c r="BJ11" s="44"/>
-      <c r="BK11" s="44"/>
-      <c r="BL11" s="44"/>
-      <c r="BM11" s="44"/>
-      <c r="BN11" s="44"/>
-      <c r="BO11" s="44"/>
-      <c r="BP11" s="44"/>
-      <c r="BQ11" s="44"/>
-      <c r="BR11" s="45"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="44"/>
-      <c r="BU11" s="47"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="44"/>
-      <c r="BX11" s="44"/>
-      <c r="BY11" s="44"/>
-      <c r="BZ11" s="44"/>
-      <c r="CA11" s="44"/>
-      <c r="CB11" s="44"/>
-      <c r="CC11" s="44"/>
-      <c r="CD11" s="44"/>
-      <c r="CE11" s="44"/>
-      <c r="CF11" s="44"/>
-      <c r="CG11" s="44"/>
-      <c r="CH11" s="44"/>
-      <c r="CI11" s="44"/>
-      <c r="CJ11" s="44"/>
-      <c r="CK11" s="44"/>
-      <c r="CL11" s="44"/>
-      <c r="CM11" s="44"/>
-      <c r="CN11" s="44"/>
-      <c r="CO11" s="44"/>
-      <c r="CP11" s="44"/>
-      <c r="CQ11" s="44"/>
-      <c r="CR11" s="44"/>
-      <c r="CS11" s="44"/>
-      <c r="CT11" s="44"/>
-      <c r="CU11" s="47"/>
-      <c r="CV11" s="46"/>
-      <c r="CW11" s="45"/>
-      <c r="CX11" s="46"/>
-      <c r="CY11" s="44"/>
-      <c r="CZ11" s="44"/>
-      <c r="DA11" s="44"/>
-      <c r="DB11" s="44"/>
-      <c r="DC11" s="44"/>
-      <c r="DD11" s="44"/>
-      <c r="DE11" s="44"/>
-      <c r="DF11" s="44"/>
-      <c r="DG11" s="44"/>
-      <c r="DH11" s="44"/>
-      <c r="DI11" s="44"/>
-      <c r="DJ11" s="44"/>
-      <c r="DK11" s="44"/>
-      <c r="DL11" s="44"/>
-      <c r="DM11" s="44"/>
-      <c r="DN11" s="44"/>
-      <c r="DO11" s="44"/>
-      <c r="DP11" s="44"/>
-      <c r="DQ11" s="44"/>
-      <c r="DR11" s="44"/>
-      <c r="DS11" s="44"/>
-      <c r="DT11" s="44"/>
-      <c r="DU11" s="44"/>
-      <c r="DV11" s="44"/>
-      <c r="DW11" s="44"/>
-      <c r="DX11" s="44"/>
-      <c r="DY11" s="44"/>
-      <c r="DZ11" s="44"/>
-      <c r="EA11" s="44"/>
-      <c r="EB11" s="45"/>
-      <c r="EC11" s="46"/>
-      <c r="ED11" s="44"/>
-      <c r="EE11" s="44"/>
-      <c r="EF11" s="44"/>
-      <c r="EG11" s="44"/>
-      <c r="EH11" s="44"/>
-      <c r="EI11" s="44"/>
-      <c r="EJ11" s="44"/>
-      <c r="EK11" s="44"/>
-      <c r="EL11" s="44"/>
-      <c r="EM11" s="44"/>
-      <c r="EN11" s="44"/>
-      <c r="EO11" s="44"/>
-      <c r="EP11" s="44"/>
-      <c r="EQ11" s="44"/>
-      <c r="ER11" s="44"/>
-      <c r="ES11" s="44"/>
-      <c r="ET11" s="44"/>
-      <c r="EU11" s="44"/>
-      <c r="EV11" s="44"/>
-      <c r="EW11" s="44"/>
-      <c r="EX11" s="44"/>
-      <c r="EY11" s="44"/>
-      <c r="EZ11" s="44"/>
-      <c r="FA11" s="44"/>
-      <c r="FB11" s="44"/>
-      <c r="FC11" s="44"/>
-      <c r="FD11" s="45"/>
-      <c r="FE11" s="46"/>
-      <c r="FF11" s="44"/>
-      <c r="FG11" s="44"/>
-      <c r="FH11" s="44"/>
-      <c r="FI11" s="44"/>
-      <c r="FJ11" s="44"/>
-      <c r="FK11" s="44"/>
-      <c r="FL11" s="44"/>
-      <c r="FM11" s="44"/>
-      <c r="FN11" s="44"/>
-      <c r="FO11" s="44"/>
-      <c r="FP11" s="44"/>
-      <c r="FQ11" s="44"/>
-      <c r="FR11" s="44"/>
-      <c r="FS11" s="44"/>
-      <c r="FT11" s="44"/>
-      <c r="FU11" s="44"/>
-      <c r="FV11" s="44"/>
-      <c r="FW11" s="44"/>
-      <c r="FX11" s="44"/>
-      <c r="FY11" s="44"/>
-      <c r="FZ11" s="44"/>
-      <c r="GA11" s="44"/>
-      <c r="GB11" s="44"/>
-      <c r="GC11" s="44"/>
-      <c r="GD11" s="44"/>
-      <c r="GE11" s="44"/>
-      <c r="GF11" s="44"/>
-      <c r="GG11" s="44"/>
-      <c r="GH11" s="44"/>
-      <c r="GI11" s="45"/>
+      <c r="H11" s="24">
+        <v>46299</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="39"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="42"/>
+      <c r="AA11" s="42"/>
+      <c r="AB11" s="42"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="42"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="42"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="42"/>
+      <c r="AK11" s="42"/>
+      <c r="AL11" s="42"/>
+      <c r="AM11" s="42"/>
+      <c r="AN11" s="43"/>
+      <c r="AO11" s="44"/>
+      <c r="AP11" s="42"/>
+      <c r="AQ11" s="42"/>
+      <c r="AR11" s="42"/>
+      <c r="AS11" s="42"/>
+      <c r="AT11" s="42"/>
+      <c r="AU11" s="42"/>
+      <c r="AV11" s="42"/>
+      <c r="AW11" s="42"/>
+      <c r="AX11" s="42"/>
+      <c r="AY11" s="42"/>
+      <c r="AZ11" s="42"/>
+      <c r="BA11" s="42"/>
+      <c r="BB11" s="42"/>
+      <c r="BC11" s="42"/>
+      <c r="BD11" s="42"/>
+      <c r="BE11" s="42"/>
+      <c r="BF11" s="42"/>
+      <c r="BG11" s="42"/>
+      <c r="BH11" s="42"/>
+      <c r="BI11" s="42"/>
+      <c r="BJ11" s="42"/>
+      <c r="BK11" s="42"/>
+      <c r="BL11" s="42"/>
+      <c r="BM11" s="42"/>
+      <c r="BN11" s="42"/>
+      <c r="BO11" s="42"/>
+      <c r="BP11" s="42"/>
+      <c r="BQ11" s="42"/>
+      <c r="BR11" s="43"/>
+      <c r="BS11" s="44"/>
+      <c r="BT11" s="42"/>
+      <c r="BU11" s="45"/>
+      <c r="BV11" s="44"/>
+      <c r="BW11" s="42"/>
+      <c r="BX11" s="42"/>
+      <c r="BY11" s="42"/>
+      <c r="BZ11" s="42"/>
+      <c r="CA11" s="42"/>
+      <c r="CB11" s="42"/>
+      <c r="CC11" s="42"/>
+      <c r="CD11" s="42"/>
+      <c r="CE11" s="42"/>
+      <c r="CF11" s="42"/>
+      <c r="CG11" s="42"/>
+      <c r="CH11" s="42"/>
+      <c r="CI11" s="42"/>
+      <c r="CJ11" s="42"/>
+      <c r="CK11" s="42"/>
+      <c r="CL11" s="42"/>
+      <c r="CM11" s="42"/>
+      <c r="CN11" s="42"/>
+      <c r="CO11" s="42"/>
+      <c r="CP11" s="42"/>
+      <c r="CQ11" s="42"/>
+      <c r="CR11" s="42"/>
+      <c r="CS11" s="42"/>
+      <c r="CT11" s="42"/>
+      <c r="CU11" s="45"/>
+      <c r="CV11" s="44"/>
+      <c r="CW11" s="43"/>
+      <c r="CX11" s="44"/>
+      <c r="CY11" s="42"/>
+      <c r="CZ11" s="42"/>
+      <c r="DA11" s="42"/>
+      <c r="DB11" s="42"/>
+      <c r="DC11" s="42"/>
+      <c r="DD11" s="42"/>
+      <c r="DE11" s="42"/>
+      <c r="DF11" s="42"/>
+      <c r="DG11" s="42"/>
+      <c r="DH11" s="42"/>
+      <c r="DI11" s="42"/>
+      <c r="DJ11" s="42"/>
+      <c r="DK11" s="42"/>
+      <c r="DL11" s="42"/>
+      <c r="DM11" s="42"/>
+      <c r="DN11" s="42"/>
+      <c r="DO11" s="42"/>
+      <c r="DP11" s="42"/>
+      <c r="DQ11" s="42"/>
+      <c r="DR11" s="42"/>
+      <c r="DS11" s="42"/>
+      <c r="DT11" s="42"/>
+      <c r="DU11" s="42"/>
+      <c r="DV11" s="42"/>
+      <c r="DW11" s="42"/>
+      <c r="DX11" s="42"/>
+      <c r="DY11" s="42"/>
+      <c r="DZ11" s="42"/>
+      <c r="EA11" s="42"/>
+      <c r="EB11" s="43"/>
+      <c r="EC11" s="44"/>
+      <c r="ED11" s="42"/>
+      <c r="EE11" s="42"/>
+      <c r="EF11" s="42"/>
+      <c r="EG11" s="42"/>
+      <c r="EH11" s="42"/>
+      <c r="EI11" s="42"/>
+      <c r="EJ11" s="42"/>
+      <c r="EK11" s="42"/>
+      <c r="EL11" s="42"/>
+      <c r="EM11" s="42"/>
+      <c r="EN11" s="42"/>
+      <c r="EO11" s="42"/>
+      <c r="EP11" s="42"/>
+      <c r="EQ11" s="42"/>
+      <c r="ER11" s="42"/>
+      <c r="ES11" s="42"/>
+      <c r="ET11" s="42"/>
+      <c r="EU11" s="42"/>
+      <c r="EV11" s="42"/>
+      <c r="EW11" s="42"/>
+      <c r="EX11" s="42"/>
+      <c r="EY11" s="42"/>
+      <c r="EZ11" s="42"/>
+      <c r="FA11" s="42"/>
+      <c r="FB11" s="42"/>
+      <c r="FC11" s="42"/>
+      <c r="FD11" s="43"/>
+      <c r="FE11" s="44"/>
+      <c r="FF11" s="42"/>
+      <c r="FG11" s="42"/>
+      <c r="FH11" s="42"/>
+      <c r="FI11" s="42"/>
+      <c r="FJ11" s="42"/>
+      <c r="FK11" s="42"/>
+      <c r="FL11" s="42"/>
+      <c r="FM11" s="42"/>
+      <c r="FN11" s="42"/>
+      <c r="FO11" s="42"/>
+      <c r="FP11" s="42"/>
+      <c r="FQ11" s="42"/>
+      <c r="FR11" s="42"/>
+      <c r="FS11" s="42"/>
+      <c r="FT11" s="42"/>
+      <c r="FU11" s="42"/>
+      <c r="FV11" s="42"/>
+      <c r="FW11" s="42"/>
+      <c r="FX11" s="42"/>
+      <c r="FY11" s="42"/>
+      <c r="FZ11" s="42"/>
+      <c r="GA11" s="42"/>
+      <c r="GB11" s="42"/>
+      <c r="GC11" s="42"/>
+      <c r="GD11" s="42"/>
+      <c r="GE11" s="42"/>
+      <c r="GF11" s="42"/>
+      <c r="GG11" s="42"/>
+      <c r="GH11" s="42"/>
+      <c r="GI11" s="43"/>
     </row>
-    <row r="12" spans="1:192" s="36" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="52"/>
+    <row r="12" spans="1:192" s="35" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="49"/>
       <c r="B12" s="3">
         <v>4</v>
       </c>
-      <c r="C12" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>13</v>
+      <c r="C12" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E12" s="34">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="F12" s="24">
-        <v>46312</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="24"/>
+        <v>46303</v>
+      </c>
+      <c r="G12" s="34">
+        <v>46303</v>
+      </c>
+      <c r="H12" s="24">
+        <v>46303</v>
+      </c>
       <c r="I12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="38"/>
-      <c r="AX12" s="38"/>
-      <c r="AY12" s="38"/>
-      <c r="AZ12" s="38"/>
-      <c r="BA12" s="38"/>
-      <c r="BB12" s="38"/>
-      <c r="BC12" s="38"/>
-      <c r="BD12" s="38"/>
-      <c r="BE12" s="38"/>
-      <c r="BF12" s="38"/>
-      <c r="BG12" s="38"/>
-      <c r="BH12" s="38"/>
-      <c r="BI12" s="38"/>
-      <c r="BJ12" s="38"/>
-      <c r="BK12" s="38"/>
-      <c r="BL12" s="38"/>
-      <c r="BM12" s="38"/>
-      <c r="BN12" s="38"/>
-      <c r="BO12" s="38"/>
-      <c r="BP12" s="38"/>
-      <c r="BQ12" s="38"/>
-      <c r="BR12" s="38"/>
-      <c r="BS12" s="38"/>
-      <c r="BT12" s="38"/>
-      <c r="BU12" s="38"/>
-      <c r="BV12" s="38"/>
-      <c r="BW12" s="38"/>
-      <c r="BX12" s="38"/>
-      <c r="BY12" s="38"/>
-      <c r="BZ12" s="38"/>
-      <c r="CA12" s="38"/>
-      <c r="CB12" s="38"/>
-      <c r="CC12" s="38"/>
-      <c r="CD12" s="38"/>
-      <c r="CE12" s="38"/>
-      <c r="CF12" s="38"/>
-      <c r="CG12" s="38"/>
-      <c r="CH12" s="38"/>
-      <c r="CI12" s="38"/>
-      <c r="CJ12" s="38"/>
-      <c r="CK12" s="38"/>
-      <c r="CL12" s="38"/>
-      <c r="CM12" s="38"/>
-      <c r="CN12" s="38"/>
-      <c r="CO12" s="38"/>
-      <c r="CP12" s="38"/>
-      <c r="CQ12" s="38"/>
-      <c r="CR12" s="38"/>
-      <c r="CS12" s="38"/>
-      <c r="CT12" s="38"/>
-      <c r="CU12" s="38"/>
-      <c r="CV12" s="38"/>
-      <c r="CW12" s="38"/>
-      <c r="CX12" s="38"/>
-      <c r="CY12" s="38"/>
-      <c r="CZ12" s="38"/>
-      <c r="DA12" s="38"/>
-      <c r="DB12" s="38"/>
-      <c r="DC12" s="38"/>
-      <c r="DD12" s="38"/>
-      <c r="DE12" s="38"/>
-      <c r="DF12" s="38"/>
-      <c r="DG12" s="38"/>
-      <c r="DH12" s="38"/>
-      <c r="DI12" s="38"/>
-      <c r="DJ12" s="38"/>
-      <c r="DK12" s="38"/>
-      <c r="DL12" s="38"/>
-      <c r="DM12" s="38"/>
-      <c r="DN12" s="38"/>
-      <c r="DO12" s="38"/>
-      <c r="DP12" s="38"/>
-      <c r="DQ12" s="38"/>
-      <c r="DR12" s="38"/>
-      <c r="DS12" s="38"/>
-      <c r="DT12" s="38"/>
-      <c r="DU12" s="38"/>
-      <c r="DV12" s="38"/>
-      <c r="DW12" s="38"/>
-      <c r="DX12" s="38"/>
-      <c r="DY12" s="38"/>
-      <c r="DZ12" s="38"/>
-      <c r="EA12" s="38"/>
-      <c r="EB12" s="38"/>
-      <c r="EC12" s="38"/>
-      <c r="ED12" s="38"/>
-      <c r="EE12" s="38"/>
-      <c r="EF12" s="38"/>
-      <c r="EG12" s="38"/>
-      <c r="EH12" s="38"/>
-      <c r="EI12" s="38"/>
-      <c r="EJ12" s="38"/>
-      <c r="EK12" s="38"/>
-      <c r="EL12" s="38"/>
-      <c r="EM12" s="38"/>
-      <c r="EN12" s="38"/>
-      <c r="EO12" s="38"/>
-      <c r="EP12" s="38"/>
-      <c r="EQ12" s="38"/>
-      <c r="ER12" s="38"/>
-      <c r="ES12" s="38"/>
-      <c r="ET12" s="38"/>
-      <c r="EU12" s="38"/>
-      <c r="EV12" s="38"/>
-      <c r="EW12" s="38"/>
-      <c r="EX12" s="38"/>
-      <c r="EY12" s="38"/>
-      <c r="EZ12" s="38"/>
-      <c r="FA12" s="38"/>
-      <c r="FB12" s="38"/>
-      <c r="FC12" s="38"/>
-      <c r="FD12" s="38"/>
-      <c r="FE12" s="38"/>
-      <c r="FF12" s="38"/>
-      <c r="FG12" s="38"/>
-      <c r="FH12" s="38"/>
-      <c r="FI12" s="38"/>
-      <c r="FJ12" s="38"/>
-      <c r="FK12" s="38"/>
-      <c r="FL12" s="38"/>
-      <c r="FM12" s="38"/>
-      <c r="FN12" s="38"/>
-      <c r="FO12" s="38"/>
-      <c r="FP12" s="38"/>
-      <c r="FQ12" s="38"/>
-      <c r="FR12" s="38"/>
-      <c r="FS12" s="38"/>
-      <c r="FT12" s="38"/>
-      <c r="FU12" s="38"/>
-      <c r="FV12" s="38"/>
-      <c r="FW12" s="38"/>
-      <c r="FX12" s="38"/>
-      <c r="FY12" s="38"/>
-      <c r="FZ12" s="38"/>
-      <c r="GA12" s="38"/>
-      <c r="GB12" s="38"/>
-      <c r="GC12" s="38"/>
-      <c r="GD12" s="38"/>
-      <c r="GE12" s="38"/>
-      <c r="GF12" s="38"/>
-      <c r="GG12" s="38"/>
-      <c r="GH12" s="38"/>
-      <c r="GI12" s="38"/>
+        <v>14</v>
+      </c>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="37"/>
+      <c r="AC12" s="37"/>
+      <c r="AD12" s="37"/>
+      <c r="AE12" s="37"/>
+      <c r="AF12" s="37"/>
+      <c r="AG12" s="37"/>
+      <c r="AH12" s="37"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="37"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="37"/>
+      <c r="AQ12" s="37"/>
+      <c r="AR12" s="37"/>
+      <c r="AS12" s="37"/>
+      <c r="AT12" s="37"/>
+      <c r="AU12" s="37"/>
+      <c r="AV12" s="37"/>
+      <c r="AW12" s="37"/>
+      <c r="AX12" s="37"/>
+      <c r="AY12" s="37"/>
+      <c r="AZ12" s="37"/>
+      <c r="BA12" s="37"/>
+      <c r="BB12" s="37"/>
+      <c r="BC12" s="37"/>
+      <c r="BD12" s="37"/>
+      <c r="BE12" s="37"/>
+      <c r="BF12" s="37"/>
+      <c r="BG12" s="37"/>
+      <c r="BH12" s="37"/>
+      <c r="BI12" s="37"/>
+      <c r="BJ12" s="37"/>
+      <c r="BK12" s="37"/>
+      <c r="BL12" s="37"/>
+      <c r="BM12" s="37"/>
+      <c r="BN12" s="37"/>
+      <c r="BO12" s="37"/>
+      <c r="BP12" s="37"/>
+      <c r="BQ12" s="37"/>
+      <c r="BR12" s="37"/>
+      <c r="BS12" s="37"/>
+      <c r="BT12" s="37"/>
+      <c r="BU12" s="37"/>
+      <c r="BV12" s="37"/>
+      <c r="BW12" s="37"/>
+      <c r="BX12" s="37"/>
+      <c r="BY12" s="37"/>
+      <c r="BZ12" s="37"/>
+      <c r="CA12" s="37"/>
+      <c r="CB12" s="37"/>
+      <c r="CC12" s="37"/>
+      <c r="CD12" s="37"/>
+      <c r="CE12" s="37"/>
+      <c r="CF12" s="37"/>
+      <c r="CG12" s="37"/>
+      <c r="CH12" s="37"/>
+      <c r="CI12" s="37"/>
+      <c r="CJ12" s="37"/>
+      <c r="CK12" s="37"/>
+      <c r="CL12" s="37"/>
+      <c r="CM12" s="37"/>
+      <c r="CN12" s="37"/>
+      <c r="CO12" s="37"/>
+      <c r="CP12" s="37"/>
+      <c r="CQ12" s="37"/>
+      <c r="CR12" s="37"/>
+      <c r="CS12" s="37"/>
+      <c r="CT12" s="37"/>
+      <c r="CU12" s="37"/>
+      <c r="CV12" s="37"/>
+      <c r="CW12" s="37"/>
+      <c r="CX12" s="37"/>
+      <c r="CY12" s="37"/>
+      <c r="CZ12" s="37"/>
+      <c r="DA12" s="37"/>
+      <c r="DB12" s="37"/>
+      <c r="DC12" s="37"/>
+      <c r="DD12" s="37"/>
+      <c r="DE12" s="37"/>
+      <c r="DF12" s="37"/>
+      <c r="DG12" s="37"/>
+      <c r="DH12" s="37"/>
+      <c r="DI12" s="37"/>
+      <c r="DJ12" s="37"/>
+      <c r="DK12" s="37"/>
+      <c r="DL12" s="37"/>
+      <c r="DM12" s="37"/>
+      <c r="DN12" s="37"/>
+      <c r="DO12" s="37"/>
+      <c r="DP12" s="37"/>
+      <c r="DQ12" s="37"/>
+      <c r="DR12" s="37"/>
+      <c r="DS12" s="37"/>
+      <c r="DT12" s="37"/>
+      <c r="DU12" s="37"/>
+      <c r="DV12" s="37"/>
+      <c r="DW12" s="37"/>
+      <c r="DX12" s="37"/>
+      <c r="DY12" s="37"/>
+      <c r="DZ12" s="37"/>
+      <c r="EA12" s="37"/>
+      <c r="EB12" s="37"/>
+      <c r="EC12" s="37"/>
+      <c r="ED12" s="37"/>
+      <c r="EE12" s="37"/>
+      <c r="EF12" s="37"/>
+      <c r="EG12" s="37"/>
+      <c r="EH12" s="37"/>
+      <c r="EI12" s="37"/>
+      <c r="EJ12" s="37"/>
+      <c r="EK12" s="37"/>
+      <c r="EL12" s="37"/>
+      <c r="EM12" s="37"/>
+      <c r="EN12" s="37"/>
+      <c r="EO12" s="37"/>
+      <c r="EP12" s="37"/>
+      <c r="EQ12" s="37"/>
+      <c r="ER12" s="37"/>
+      <c r="ES12" s="37"/>
+      <c r="ET12" s="37"/>
+      <c r="EU12" s="37"/>
+      <c r="EV12" s="37"/>
+      <c r="EW12" s="37"/>
+      <c r="EX12" s="37"/>
+      <c r="EY12" s="37"/>
+      <c r="EZ12" s="37"/>
+      <c r="FA12" s="37"/>
+      <c r="FB12" s="37"/>
+      <c r="FC12" s="37"/>
+      <c r="FD12" s="37"/>
+      <c r="FE12" s="37"/>
+      <c r="FF12" s="37"/>
+      <c r="FG12" s="37"/>
+      <c r="FH12" s="37"/>
+      <c r="FI12" s="37"/>
+      <c r="FJ12" s="37"/>
+      <c r="FK12" s="37"/>
+      <c r="FL12" s="37"/>
+      <c r="FM12" s="37"/>
+      <c r="FN12" s="37"/>
+      <c r="FO12" s="37"/>
+      <c r="FP12" s="37"/>
+      <c r="FQ12" s="37"/>
+      <c r="FR12" s="37"/>
+      <c r="FS12" s="37"/>
+      <c r="FT12" s="37"/>
+      <c r="FU12" s="37"/>
+      <c r="FV12" s="37"/>
+      <c r="FW12" s="37"/>
+      <c r="FX12" s="37"/>
+      <c r="FY12" s="37"/>
+      <c r="FZ12" s="37"/>
+      <c r="GA12" s="37"/>
+      <c r="GB12" s="37"/>
+      <c r="GC12" s="37"/>
+      <c r="GD12" s="37"/>
+      <c r="GE12" s="37"/>
+      <c r="GF12" s="37"/>
+      <c r="GG12" s="37"/>
+      <c r="GH12" s="37"/>
+      <c r="GI12" s="37"/>
     </row>
     <row r="13" spans="1:192" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="26"/>
-      <c r="B13" s="35">
+      <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="55">
-        <v>46313</v>
-      </c>
-      <c r="F13" s="56">
-        <v>46326</v>
-      </c>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="35" t="s">
-        <v>20</v>
+      <c r="C13" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="34">
+        <v>46304</v>
+      </c>
+      <c r="F13" s="24">
+        <v>46304</v>
+      </c>
+      <c r="G13" s="34">
+        <v>46304</v>
+      </c>
+      <c r="H13" s="24">
+        <v>46304</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="J13" s="32"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="49"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
-      <c r="AL13" s="49"/>
-      <c r="AM13" s="49"/>
-      <c r="AN13" s="50"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="46"/>
+      <c r="Y13" s="46"/>
+      <c r="Z13" s="46"/>
+      <c r="AA13" s="46"/>
+      <c r="AB13" s="46"/>
+      <c r="AC13" s="46"/>
+      <c r="AD13" s="46"/>
+      <c r="AE13" s="46"/>
+      <c r="AF13" s="46"/>
+      <c r="AG13" s="46"/>
+      <c r="AH13" s="46"/>
+      <c r="AI13" s="46"/>
+      <c r="AJ13" s="46"/>
+      <c r="AK13" s="46"/>
+      <c r="AL13" s="46"/>
+      <c r="AM13" s="46"/>
+      <c r="AN13" s="47"/>
       <c r="AO13" s="32"/>
-      <c r="AP13" s="49"/>
-      <c r="AQ13" s="49"/>
-      <c r="AR13" s="49"/>
-      <c r="AS13" s="49"/>
-      <c r="AT13" s="49"/>
-      <c r="AU13" s="49"/>
-      <c r="AV13" s="49"/>
-      <c r="AW13" s="49"/>
-      <c r="AX13" s="49"/>
-      <c r="AY13" s="49"/>
-      <c r="AZ13" s="49"/>
-      <c r="BA13" s="49"/>
-      <c r="BB13" s="49"/>
-      <c r="BC13" s="49"/>
-      <c r="BD13" s="49"/>
-      <c r="BE13" s="49"/>
-      <c r="BF13" s="49"/>
-      <c r="BG13" s="49"/>
-      <c r="BH13" s="49"/>
-      <c r="BI13" s="49"/>
-      <c r="BJ13" s="49"/>
-      <c r="BK13" s="49"/>
-      <c r="BL13" s="49"/>
-      <c r="BM13" s="49"/>
-      <c r="BN13" s="49"/>
-      <c r="BO13" s="49"/>
-      <c r="BP13" s="49"/>
-      <c r="BQ13" s="49"/>
-      <c r="BR13" s="50"/>
+      <c r="AP13" s="46"/>
+      <c r="AQ13" s="46"/>
+      <c r="AR13" s="46"/>
+      <c r="AS13" s="46"/>
+      <c r="AT13" s="46"/>
+      <c r="AU13" s="46"/>
+      <c r="AV13" s="46"/>
+      <c r="AW13" s="46"/>
+      <c r="AX13" s="46"/>
+      <c r="AY13" s="46"/>
+      <c r="AZ13" s="46"/>
+      <c r="BA13" s="46"/>
+      <c r="BB13" s="46"/>
+      <c r="BC13" s="46"/>
+      <c r="BD13" s="46"/>
+      <c r="BE13" s="46"/>
+      <c r="BF13" s="46"/>
+      <c r="BG13" s="46"/>
+      <c r="BH13" s="46"/>
+      <c r="BI13" s="46"/>
+      <c r="BJ13" s="46"/>
+      <c r="BK13" s="46"/>
+      <c r="BL13" s="46"/>
+      <c r="BM13" s="46"/>
+      <c r="BN13" s="46"/>
+      <c r="BO13" s="46"/>
+      <c r="BP13" s="46"/>
+      <c r="BQ13" s="46"/>
+      <c r="BR13" s="47"/>
       <c r="BS13" s="32"/>
-      <c r="BT13" s="49"/>
-      <c r="BU13" s="51"/>
+      <c r="BT13" s="46"/>
+      <c r="BU13" s="48"/>
       <c r="BV13" s="32"/>
-      <c r="BW13" s="49"/>
-      <c r="BX13" s="49"/>
-      <c r="BY13" s="49"/>
-      <c r="BZ13" s="49"/>
-      <c r="CA13" s="49"/>
-      <c r="CB13" s="49"/>
-      <c r="CC13" s="49"/>
-      <c r="CD13" s="49"/>
-      <c r="CE13" s="49"/>
-      <c r="CF13" s="49"/>
-      <c r="CG13" s="49"/>
-      <c r="CH13" s="49"/>
-      <c r="CI13" s="49"/>
-      <c r="CJ13" s="49"/>
-      <c r="CK13" s="49"/>
-      <c r="CL13" s="49"/>
-      <c r="CM13" s="49"/>
-      <c r="CN13" s="49"/>
-      <c r="CO13" s="49"/>
-      <c r="CP13" s="49"/>
-      <c r="CQ13" s="49"/>
-      <c r="CR13" s="49"/>
-      <c r="CS13" s="49"/>
-      <c r="CT13" s="49"/>
-      <c r="CU13" s="51"/>
+      <c r="BW13" s="46"/>
+      <c r="BX13" s="46"/>
+      <c r="BY13" s="46"/>
+      <c r="BZ13" s="46"/>
+      <c r="CA13" s="46"/>
+      <c r="CB13" s="46"/>
+      <c r="CC13" s="46"/>
+      <c r="CD13" s="46"/>
+      <c r="CE13" s="46"/>
+      <c r="CF13" s="46"/>
+      <c r="CG13" s="46"/>
+      <c r="CH13" s="46"/>
+      <c r="CI13" s="46"/>
+      <c r="CJ13" s="46"/>
+      <c r="CK13" s="46"/>
+      <c r="CL13" s="46"/>
+      <c r="CM13" s="46"/>
+      <c r="CN13" s="46"/>
+      <c r="CO13" s="46"/>
+      <c r="CP13" s="46"/>
+      <c r="CQ13" s="46"/>
+      <c r="CR13" s="46"/>
+      <c r="CS13" s="46"/>
+      <c r="CT13" s="46"/>
+      <c r="CU13" s="48"/>
       <c r="CV13" s="32"/>
-      <c r="CW13" s="50"/>
+      <c r="CW13" s="47"/>
       <c r="CX13" s="32"/>
-      <c r="CY13" s="49"/>
-      <c r="CZ13" s="49"/>
-      <c r="DA13" s="49"/>
-      <c r="DB13" s="49"/>
-      <c r="DC13" s="49"/>
-      <c r="DD13" s="49"/>
-      <c r="DE13" s="49"/>
-      <c r="DF13" s="49"/>
-      <c r="DG13" s="49"/>
-      <c r="DH13" s="49"/>
-      <c r="DI13" s="49"/>
-      <c r="DJ13" s="49"/>
-      <c r="DK13" s="49"/>
-      <c r="DL13" s="49"/>
-      <c r="DM13" s="49"/>
-      <c r="DN13" s="49"/>
-      <c r="DO13" s="49"/>
-      <c r="DP13" s="49"/>
-      <c r="DQ13" s="49"/>
-      <c r="DR13" s="49"/>
-      <c r="DS13" s="49"/>
-      <c r="DT13" s="49"/>
-      <c r="DU13" s="49"/>
-      <c r="DV13" s="49"/>
-      <c r="DW13" s="49"/>
-      <c r="DX13" s="49"/>
-      <c r="DY13" s="49"/>
-      <c r="DZ13" s="49"/>
-      <c r="EA13" s="49"/>
-      <c r="EB13" s="50"/>
+      <c r="CY13" s="46"/>
+      <c r="CZ13" s="46"/>
+      <c r="DA13" s="46"/>
+      <c r="DB13" s="46"/>
+      <c r="DC13" s="46"/>
+      <c r="DD13" s="46"/>
+      <c r="DE13" s="46"/>
+      <c r="DF13" s="46"/>
+      <c r="DG13" s="46"/>
+      <c r="DH13" s="46"/>
+      <c r="DI13" s="46"/>
+      <c r="DJ13" s="46"/>
+      <c r="DK13" s="46"/>
+      <c r="DL13" s="46"/>
+      <c r="DM13" s="46"/>
+      <c r="DN13" s="46"/>
+      <c r="DO13" s="46"/>
+      <c r="DP13" s="46"/>
+      <c r="DQ13" s="46"/>
+      <c r="DR13" s="46"/>
+      <c r="DS13" s="46"/>
+      <c r="DT13" s="46"/>
+      <c r="DU13" s="46"/>
+      <c r="DV13" s="46"/>
+      <c r="DW13" s="46"/>
+      <c r="DX13" s="46"/>
+      <c r="DY13" s="46"/>
+      <c r="DZ13" s="46"/>
+      <c r="EA13" s="46"/>
+      <c r="EB13" s="47"/>
       <c r="EC13" s="32"/>
-      <c r="ED13" s="49"/>
-      <c r="EE13" s="49"/>
-      <c r="EF13" s="49"/>
-      <c r="EG13" s="49"/>
-      <c r="EH13" s="49"/>
-      <c r="EI13" s="49"/>
-      <c r="EJ13" s="49"/>
-      <c r="EK13" s="49"/>
-      <c r="EL13" s="49"/>
-      <c r="EM13" s="49"/>
-      <c r="EN13" s="49"/>
-      <c r="EO13" s="49"/>
-      <c r="EP13" s="49"/>
-      <c r="EQ13" s="49"/>
-      <c r="ER13" s="49"/>
-      <c r="ES13" s="49"/>
-      <c r="ET13" s="49"/>
-      <c r="EU13" s="49"/>
-      <c r="EV13" s="49"/>
-      <c r="EW13" s="49"/>
-      <c r="EX13" s="49"/>
-      <c r="EY13" s="49"/>
-      <c r="EZ13" s="49"/>
-      <c r="FA13" s="49"/>
-      <c r="FB13" s="49"/>
-      <c r="FC13" s="49"/>
-      <c r="FD13" s="50"/>
+      <c r="ED13" s="46"/>
+      <c r="EE13" s="46"/>
+      <c r="EF13" s="46"/>
+      <c r="EG13" s="46"/>
+      <c r="EH13" s="46"/>
+      <c r="EI13" s="46"/>
+      <c r="EJ13" s="46"/>
+      <c r="EK13" s="46"/>
+      <c r="EL13" s="46"/>
+      <c r="EM13" s="46"/>
+      <c r="EN13" s="46"/>
+      <c r="EO13" s="46"/>
+      <c r="EP13" s="46"/>
+      <c r="EQ13" s="46"/>
+      <c r="ER13" s="46"/>
+      <c r="ES13" s="46"/>
+      <c r="ET13" s="46"/>
+      <c r="EU13" s="46"/>
+      <c r="EV13" s="46"/>
+      <c r="EW13" s="46"/>
+      <c r="EX13" s="46"/>
+      <c r="EY13" s="46"/>
+      <c r="EZ13" s="46"/>
+      <c r="FA13" s="46"/>
+      <c r="FB13" s="46"/>
+      <c r="FC13" s="46"/>
+      <c r="FD13" s="47"/>
       <c r="FE13" s="32"/>
-      <c r="FF13" s="49"/>
-      <c r="FG13" s="49"/>
-      <c r="FH13" s="49"/>
-      <c r="FI13" s="49"/>
-      <c r="FJ13" s="49"/>
-      <c r="FK13" s="49"/>
-      <c r="FL13" s="49"/>
-      <c r="FM13" s="49"/>
-      <c r="FN13" s="49"/>
-      <c r="FO13" s="49"/>
-      <c r="FP13" s="49"/>
-      <c r="FQ13" s="49"/>
-      <c r="FR13" s="49"/>
-      <c r="FS13" s="49"/>
-      <c r="FT13" s="49"/>
-      <c r="FU13" s="49"/>
-      <c r="FV13" s="49"/>
-      <c r="FW13" s="49"/>
-      <c r="FX13" s="49"/>
-      <c r="FY13" s="49"/>
-      <c r="FZ13" s="49"/>
-      <c r="GA13" s="49"/>
-      <c r="GB13" s="49"/>
-      <c r="GC13" s="49"/>
-      <c r="GD13" s="49"/>
-      <c r="GE13" s="49"/>
-      <c r="GF13" s="49"/>
-      <c r="GG13" s="49"/>
-      <c r="GH13" s="49"/>
-      <c r="GI13" s="50"/>
+      <c r="FF13" s="46"/>
+      <c r="FG13" s="46"/>
+      <c r="FH13" s="46"/>
+      <c r="FI13" s="46"/>
+      <c r="FJ13" s="46"/>
+      <c r="FK13" s="46"/>
+      <c r="FL13" s="46"/>
+      <c r="FM13" s="46"/>
+      <c r="FN13" s="46"/>
+      <c r="FO13" s="46"/>
+      <c r="FP13" s="46"/>
+      <c r="FQ13" s="46"/>
+      <c r="FR13" s="46"/>
+      <c r="FS13" s="46"/>
+      <c r="FT13" s="46"/>
+      <c r="FU13" s="46"/>
+      <c r="FV13" s="46"/>
+      <c r="FW13" s="46"/>
+      <c r="FX13" s="46"/>
+      <c r="FY13" s="46"/>
+      <c r="FZ13" s="46"/>
+      <c r="GA13" s="46"/>
+      <c r="GB13" s="46"/>
+      <c r="GC13" s="46"/>
+      <c r="GD13" s="46"/>
+      <c r="GE13" s="46"/>
+      <c r="GF13" s="46"/>
+      <c r="GG13" s="46"/>
+      <c r="GH13" s="46"/>
+      <c r="GI13" s="47"/>
     </row>
     <row r="14" spans="1:192" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
       <c r="B14" s="3">
         <v>6</v>
       </c>
-      <c r="C14" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>13</v>
+      <c r="C14" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E14" s="34">
-        <v>46327</v>
+        <v>46304</v>
       </c>
       <c r="F14" s="24">
-        <v>46347</v>
-      </c>
-      <c r="G14" s="24"/>
+        <v>46307</v>
+      </c>
+      <c r="G14" s="34">
+        <v>46304</v>
+      </c>
       <c r="H14" s="24"/>
       <c r="I14" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="5"/>
@@ -6731,22 +6994,22 @@
       <c r="B15" s="3">
         <v>7</v>
       </c>
-      <c r="C15" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>13</v>
+      <c r="C15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E15" s="34">
-        <v>46348</v>
+        <v>46308</v>
       </c>
       <c r="F15" s="24">
-        <v>46361</v>
-      </c>
-      <c r="G15" s="24"/>
+        <v>46314</v>
+      </c>
+      <c r="G15" s="34"/>
       <c r="H15" s="24"/>
       <c r="I15" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="5"/>
@@ -6936,22 +7199,22 @@
       <c r="B16" s="3">
         <v>8</v>
       </c>
-      <c r="C16" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>13</v>
+      <c r="C16" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E16" s="34">
-        <v>46362</v>
+        <v>46315</v>
       </c>
       <c r="F16" s="24">
-        <v>46382</v>
-      </c>
-      <c r="G16" s="24"/>
+        <v>46326</v>
+      </c>
+      <c r="G16" s="34"/>
       <c r="H16" s="24"/>
       <c r="I16" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="5"/>
@@ -7141,22 +7404,22 @@
       <c r="B17" s="3">
         <v>9</v>
       </c>
-      <c r="C17" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>13</v>
+      <c r="C17" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E17" s="34">
-        <v>46383</v>
+        <v>46327</v>
       </c>
       <c r="F17" s="24">
-        <v>46396</v>
-      </c>
-      <c r="G17" s="24"/>
+        <v>46347</v>
+      </c>
+      <c r="G17" s="34"/>
       <c r="H17" s="24"/>
       <c r="I17" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="5"/>
@@ -7346,22 +7609,22 @@
       <c r="B18" s="3">
         <v>10</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>13</v>
-      </c>
       <c r="E18" s="34">
-        <v>46397</v>
+        <v>46348</v>
       </c>
       <c r="F18" s="24">
-        <v>46410</v>
-      </c>
-      <c r="G18" s="24"/>
+        <v>46361</v>
+      </c>
+      <c r="G18" s="34"/>
       <c r="H18" s="24"/>
       <c r="I18" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="5"/>
@@ -7551,22 +7814,22 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>13</v>
+      <c r="C19" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E19" s="34">
-        <v>46411</v>
+        <v>46362</v>
       </c>
       <c r="F19" s="24">
-        <v>46424</v>
-      </c>
-      <c r="G19" s="24"/>
+        <v>46382</v>
+      </c>
+      <c r="G19" s="34"/>
       <c r="H19" s="24"/>
       <c r="I19" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="5"/>
@@ -7756,22 +8019,22 @@
       <c r="B20" s="3">
         <v>12</v>
       </c>
-      <c r="C20" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>13</v>
+      <c r="C20" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="E20" s="34">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="F20" s="24">
-        <v>46446</v>
-      </c>
-      <c r="G20" s="24"/>
+        <v>46396</v>
+      </c>
+      <c r="G20" s="34"/>
       <c r="H20" s="24"/>
       <c r="I20" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="5"/>
@@ -7958,14 +8221,26 @@
     </row>
     <row r="21" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="26"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
+      <c r="B21" s="3">
+        <v>13</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="34">
+        <v>46397</v>
+      </c>
+      <c r="F21" s="24">
+        <v>46410</v>
+      </c>
+      <c r="G21" s="34"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -8151,14 +8426,26 @@
     </row>
     <row r="22" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="26"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="B22" s="3">
+        <v>14</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="34">
+        <v>46411</v>
+      </c>
+      <c r="F22" s="24">
+        <v>46424</v>
+      </c>
+      <c r="G22" s="34"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -8344,14 +8631,26 @@
     </row>
     <row r="23" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="26"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="B23" s="3">
+        <v>15</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="34">
+        <v>46425</v>
+      </c>
+      <c r="F23" s="24">
+        <v>46446</v>
+      </c>
+      <c r="G23" s="34"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -8538,8 +8837,8 @@
     <row r="24" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="26"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="39"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="38"/>
       <c r="E24" s="34"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
@@ -8731,8 +9030,8 @@
     <row r="25" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="26"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="39"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="34"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
@@ -8924,8 +9223,8 @@
     <row r="26" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="26"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="39"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="38"/>
       <c r="E26" s="34"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
@@ -9117,8 +9416,8 @@
     <row r="27" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="26"/>
       <c r="B27" s="3"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="39"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="34"/>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
@@ -9310,8 +9609,8 @@
     <row r="28" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="26"/>
       <c r="B28" s="3"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="39"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="34"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
@@ -9503,8 +9802,8 @@
     <row r="29" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="26"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="39"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="34"/>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
@@ -9696,8 +9995,8 @@
     <row r="30" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="26"/>
       <c r="B30" s="3"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="39"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="34"/>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
@@ -9889,8 +10188,8 @@
     <row r="31" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="26"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="39"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="38"/>
       <c r="E31" s="34"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
@@ -10082,8 +10381,8 @@
     <row r="32" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="26"/>
       <c r="B32" s="3"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="39"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="38"/>
       <c r="E32" s="34"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
@@ -10275,8 +10574,8 @@
     <row r="33" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="26"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="39"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="38"/>
       <c r="E33" s="34"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
@@ -10468,8 +10767,8 @@
     <row r="34" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="26"/>
       <c r="B34" s="3"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="39"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="38"/>
       <c r="E34" s="34"/>
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
@@ -10661,8 +10960,8 @@
     <row r="35" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="26"/>
       <c r="B35" s="3"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="39"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="38"/>
       <c r="E35" s="34"/>
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
@@ -10854,8 +11153,8 @@
     <row r="36" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="26"/>
       <c r="B36" s="3"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="39"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="38"/>
       <c r="E36" s="34"/>
       <c r="F36" s="24"/>
       <c r="G36" s="24"/>
@@ -11047,8 +11346,8 @@
     <row r="37" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="26"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="39"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="38"/>
       <c r="E37" s="34"/>
       <c r="F37" s="24"/>
       <c r="G37" s="24"/>
@@ -11240,8 +11539,8 @@
     <row r="38" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="26"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="39"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="38"/>
       <c r="E38" s="34"/>
       <c r="F38" s="24"/>
       <c r="G38" s="24"/>
@@ -11433,8 +11732,8 @@
     <row r="39" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="26"/>
       <c r="B39" s="3"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="39"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="38"/>
       <c r="E39" s="34"/>
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
@@ -11626,8 +11925,8 @@
     <row r="40" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="26"/>
       <c r="B40" s="3"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="39"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="38"/>
       <c r="E40" s="34"/>
       <c r="F40" s="24"/>
       <c r="G40" s="24"/>
@@ -11819,8 +12118,8 @@
     <row r="41" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="26"/>
       <c r="B41" s="3"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="39"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="38"/>
       <c r="E41" s="34"/>
       <c r="F41" s="24"/>
       <c r="G41" s="24"/>
@@ -12012,8 +12311,8 @@
     <row r="42" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="26"/>
       <c r="B42" s="3"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="39"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="38"/>
       <c r="E42" s="34"/>
       <c r="F42" s="24"/>
       <c r="G42" s="24"/>
@@ -12205,8 +12504,8 @@
     <row r="43" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="26"/>
       <c r="B43" s="3"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="39"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="38"/>
       <c r="E43" s="34"/>
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
@@ -12398,8 +12697,8 @@
     <row r="44" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="26"/>
       <c r="B44" s="3"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="39"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="38"/>
       <c r="E44" s="34"/>
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
@@ -12591,8 +12890,8 @@
     <row r="45" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="26"/>
       <c r="B45" s="3"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="39"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="38"/>
       <c r="E45" s="34"/>
       <c r="F45" s="24"/>
       <c r="G45" s="24"/>
@@ -12784,8 +13083,8 @@
     <row r="46" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="26"/>
       <c r="B46" s="3"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="39"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="38"/>
       <c r="E46" s="34"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
@@ -12977,8 +13276,8 @@
     <row r="47" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="26"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="39"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="38"/>
       <c r="E47" s="34"/>
       <c r="F47" s="24"/>
       <c r="G47" s="24"/>
@@ -13170,8 +13469,8 @@
     <row r="48" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="26"/>
       <c r="B48" s="3"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="39"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="38"/>
       <c r="E48" s="34"/>
       <c r="F48" s="24"/>
       <c r="G48" s="24"/>
@@ -13363,8 +13662,8 @@
     <row r="49" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="26"/>
       <c r="B49" s="3"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="39"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="38"/>
       <c r="E49" s="34"/>
       <c r="F49" s="24"/>
       <c r="G49" s="24"/>
@@ -13556,8 +13855,8 @@
     <row r="50" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="26"/>
       <c r="B50" s="3"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="39"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="38"/>
       <c r="E50" s="34"/>
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
@@ -13749,8 +14048,8 @@
     <row r="51" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="26"/>
       <c r="B51" s="3"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="39"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="38"/>
       <c r="E51" s="34"/>
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
@@ -13942,8 +14241,8 @@
     <row r="52" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="26"/>
       <c r="B52" s="3"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="39"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="38"/>
       <c r="E52" s="34"/>
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
@@ -14135,8 +14434,8 @@
     <row r="53" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="26"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="39"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="38"/>
       <c r="E53" s="34"/>
       <c r="F53" s="24"/>
       <c r="G53" s="24"/>
@@ -14328,8 +14627,8 @@
     <row r="54" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="26"/>
       <c r="B54" s="3"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="39"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="38"/>
       <c r="E54" s="34"/>
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
@@ -14521,8 +14820,8 @@
     <row r="55" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="26"/>
       <c r="B55" s="3"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="39"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="38"/>
       <c r="E55" s="34"/>
       <c r="F55" s="24"/>
       <c r="G55" s="24"/>
@@ -14714,8 +15013,8 @@
     <row r="56" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="26"/>
       <c r="B56" s="3"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="39"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="38"/>
       <c r="E56" s="34"/>
       <c r="F56" s="24"/>
       <c r="G56" s="24"/>
@@ -14907,8 +15206,8 @@
     <row r="57" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="26"/>
       <c r="B57" s="3"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="39"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="38"/>
       <c r="E57" s="34"/>
       <c r="F57" s="24"/>
       <c r="G57" s="24"/>
@@ -15100,8 +15399,8 @@
     <row r="58" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="26"/>
       <c r="B58" s="3"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="39"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="38"/>
       <c r="E58" s="34"/>
       <c r="F58" s="24"/>
       <c r="G58" s="24"/>
@@ -15293,8 +15592,8 @@
     <row r="59" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="26"/>
       <c r="B59" s="3"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="39"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="38"/>
       <c r="E59" s="34"/>
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
@@ -15486,8 +15785,8 @@
     <row r="60" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="26"/>
       <c r="B60" s="3"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="39"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="38"/>
       <c r="E60" s="34"/>
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
@@ -15679,8 +15978,8 @@
     <row r="61" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="26"/>
       <c r="B61" s="3"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="39"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="38"/>
       <c r="E61" s="34"/>
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
@@ -15872,8 +16171,8 @@
     <row r="62" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="26"/>
       <c r="B62" s="3"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="39"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="38"/>
       <c r="E62" s="34"/>
       <c r="F62" s="24"/>
       <c r="G62" s="24"/>
@@ -16065,8 +16364,8 @@
     <row r="63" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="26"/>
       <c r="B63" s="3"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="39"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="38"/>
       <c r="E63" s="34"/>
       <c r="F63" s="24"/>
       <c r="G63" s="24"/>
@@ -16258,8 +16557,8 @@
     <row r="64" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="26"/>
       <c r="B64" s="3"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="39"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="38"/>
       <c r="E64" s="34"/>
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
@@ -16451,8 +16750,8 @@
     <row r="65" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="26"/>
       <c r="B65" s="3"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="39"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="38"/>
       <c r="E65" s="34"/>
       <c r="F65" s="24"/>
       <c r="G65" s="24"/>
@@ -16644,8 +16943,8 @@
     <row r="66" spans="1:191" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="26"/>
       <c r="B66" s="3"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="39"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="38"/>
       <c r="E66" s="34"/>
       <c r="F66" s="24"/>
       <c r="G66" s="24"/>
@@ -16837,17 +17136,6 @@
   </sheetData>
   <autoFilter ref="A8:GJ10" xr:uid="{B3BDCDCE-14BB-4E1E-8D8F-50B8931AC441}"/>
   <mergeCells count="27">
-    <mergeCell ref="CX5:GI5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J6:AN6"/>
-    <mergeCell ref="AO6:BR6"/>
-    <mergeCell ref="BS6:CW6"/>
-    <mergeCell ref="CX6:EB6"/>
-    <mergeCell ref="EC6:FD6"/>
-    <mergeCell ref="FE6:GI6"/>
     <mergeCell ref="U2:X2"/>
     <mergeCell ref="U3:X3"/>
     <mergeCell ref="AE2:AH2"/>
@@ -16864,6 +17152,17 @@
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="J5:CW5"/>
+    <mergeCell ref="CX5:GI5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J6:AN6"/>
+    <mergeCell ref="AO6:BR6"/>
+    <mergeCell ref="BS6:CW6"/>
+    <mergeCell ref="CX6:EB6"/>
+    <mergeCell ref="EC6:FD6"/>
+    <mergeCell ref="FE6:GI6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="J6 AO6 BS6 CX6 EC6 FE6">
